--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>129013194</v>
       </c>
       <c r="B9" t="n">
-        <v>56840</v>
+        <v>56907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,6 +1623,16 @@
         </is>
       </c>
       <c r="AT9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
         <is>
           <t>2025</t>
         </is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>129013194</v>
       </c>
       <c r="B9" t="n">
-        <v>56907</v>
+        <v>56917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>129013194</v>
       </c>
       <c r="B9" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>129013194</v>
       </c>
       <c r="B9" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
